--- a/data/processed/harmonization/Isotopes__Radiocarbon_age/harmonized.xlsx
+++ b/data/processed/harmonization/Isotopes__Radiocarbon_age/harmonized.xlsx
@@ -432,7 +432,7 @@
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1966,12 +1966,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Hu:5:-20--10</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Hu:5:-30--20</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2538,12 +2538,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3682,12 +3682,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4722,12 +4722,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5606,12 +5606,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6074,12 +6074,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7166,12 +7166,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7270,12 +7270,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>19:20-24</t>
+          <t>Hu:19:20-24</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8466,12 +8466,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8622,12 +8622,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
